--- a/import/tb_brand1.xlsx
+++ b/import/tb_brand1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/import/tb_brand1.xlsx
+++ b/import/tb_brand1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raffle_slot\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DD5368-244A-453A-8D69-C74DCDD6BB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087627FB-355F-4040-A861-4B9411D964B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>XPENG,KIA</t>
+  </si>
+  <si>
+    <t>priority_brand</t>
   </si>
 </sst>
 </file>
@@ -454,16 +457,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="75.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,8 +480,11 @@
       <c r="D1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -488,7 +495,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -499,7 +506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -513,7 +520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -527,7 +534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -541,7 +548,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -555,7 +562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -566,7 +573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -577,7 +584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -591,7 +598,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -602,7 +609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -616,7 +623,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -630,7 +637,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -641,7 +648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -652,7 +659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>

--- a/import/tb_brand1.xlsx
+++ b/import/tb_brand1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raffle_slot\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087627FB-355F-4040-A861-4B9411D964B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF4B8EA-32CB-4E61-94AB-0DC8C27BF953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Nissan</t>
   </si>
   <si>
-    <t>Indomobil</t>
-  </si>
-  <si>
     <t>AION</t>
   </si>
   <si>
@@ -117,25 +114,34 @@
     <t>Maxus</t>
   </si>
   <si>
-    <t>Sokonindo,MG,Volvo</t>
-  </si>
-  <si>
-    <t>Sokonindo,MG</t>
-  </si>
-  <si>
-    <t>BAIC,Subaru,Ford</t>
-  </si>
-  <si>
-    <t>GWM,Audi - VW,Maxus</t>
-  </si>
-  <si>
-    <t>BAIC,Subaru,Ford,Aletra</t>
-  </si>
-  <si>
-    <t>XPENG,KIA</t>
-  </si>
-  <si>
     <t>priority_brand</t>
+  </si>
+  <si>
+    <t>Farizon</t>
+  </si>
+  <si>
+    <t>Sokonindo,Ford</t>
+  </si>
+  <si>
+    <t>Sokonindo,Ford,MG</t>
+  </si>
+  <si>
+    <t>BAIC,Subaru,Aletra</t>
+  </si>
+  <si>
+    <t>GWM,KIA,Maxus</t>
+  </si>
+  <si>
+    <t>Hyundai,XPENG,Polytron</t>
+  </si>
+  <si>
+    <t>GWM,KIA</t>
+  </si>
+  <si>
+    <t>Isuzu,BAIC,Subaru,Aletra,Farizon</t>
+  </si>
+  <si>
+    <t>Hyundai,XPENG,Polytron,Volvo</t>
   </si>
 </sst>
 </file>
@@ -463,7 +469,7 @@
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -481,7 +487,7 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -494,6 +500,9 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -505,6 +514,12 @@
       <c r="C3" t="s">
         <v>3</v>
       </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -517,7 +532,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -531,7 +546,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -539,13 +554,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -553,13 +568,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -572,6 +587,12 @@
       <c r="C8" t="s">
         <v>3</v>
       </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -583,6 +604,9 @@
       <c r="C9" t="s">
         <v>3</v>
       </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -595,7 +619,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -608,6 +632,12 @@
       <c r="C11" t="s">
         <v>4</v>
       </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -620,7 +650,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -628,13 +658,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -642,10 +672,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -653,10 +686,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -664,16 +700,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -684,10 +720,10 @@
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -698,7 +734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -709,40 +745,43 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -756,18 +795,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
